--- a/artfynd/A 51072-2021 artfynd.xlsx
+++ b/artfynd/A 51072-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51072-2021 artfynd.xlsx
+++ b/artfynd/A 51072-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>54203208</v>
+        <v>60096839</v>
       </c>
       <c r="B2" t="n">
-        <v>42543</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102923</v>
+        <v>100679</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettkantad guldvinge</t>
+          <t>Brun gräsfjäril</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycaena hippothoe</t>
+          <t>Coenonympha hero</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -724,17 +719,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>T-korsningen norr om Örtenbråten, Mölnbackaområdet, Vrm</t>
+          <t>Lundby, Butorp, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>421760.2792028901</v>
+        <v>421846</v>
       </c>
       <c r="R2" t="n">
-        <v>6619116.599465392</v>
+        <v>6619328</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,27 +753,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-07-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-06-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-07-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ängen söder om korsningen</t>
+          <t>2016-06-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,49 +773,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Gustafsson</t>
+          <t>Stina Eriksson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Gustafsson, Jenny Sander</t>
+          <t>Stina Eriksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>60096832</v>
+        <v>94363122</v>
       </c>
       <c r="B3" t="n">
-        <v>42543</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102923</v>
+        <v>102626</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettkantad guldvinge</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycaena hippothoe</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1760)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -843,36 +818,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lundby, Butorp, Vrm</t>
+          <t>Forshaga, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>421846.1290564151</v>
+        <v>421623</v>
       </c>
       <c r="R3" t="n">
-        <v>6619328.339133467</v>
+        <v>6618956</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -896,22 +861,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-06-12</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-06-12</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,53 +887,43 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Brynmiljö mot  extensiv vall med gökblomster, äkta förgätmigej, skogsnäva, humleblomster.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Stina Eriksson</t>
+          <t>Fredric Stävenborg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stina Eriksson</t>
+          <t>Fredric Stävenborg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>60096839</v>
+        <v>54203208</v>
       </c>
       <c r="B4" t="n">
-        <v>42743</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43251</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100679</v>
+        <v>102923</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brun gräsfjäril</t>
+          <t>Violettkantad guldvinge</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Coenonympha hero</t>
+          <t>Lycaena hippothoe</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -978,7 +933,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -992,17 +947,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lundby, Butorp, Vrm</t>
+          <t>T-korsningen norr om Örtenbråten, Mölnbackaområdet, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>421846.1290564151</v>
+        <v>421760</v>
       </c>
       <c r="R4" t="n">
-        <v>6619328.339133467</v>
+        <v>6619117</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1026,22 +981,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-06-12</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-06-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ängen söder om korsningen</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,15 +1006,475 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Per Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per Gustafsson, Jenny Sander</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>60096832</v>
+      </c>
+      <c r="B5" t="n">
+        <v>43251</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102923</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Violettkantad guldvinge</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycaena hippothoe</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lundby, Butorp, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>421846</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6619328</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Forshaga</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Övre Ullerud</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2016-06-12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2016-06-12</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Brynmiljö mot  extensiv vall med gökblomster, äkta förgätmigej, skogsnäva, humleblomster.</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Stina Eriksson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Stina Eriksson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>54203219</v>
+      </c>
+      <c r="B6" t="n">
+        <v>43219</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>201028</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mindre tåtelsmygare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Thymelicus lineola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ochsenheimer, 1808)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>T-korsningen norr om Örtenbråten, Mölnbackaområdet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>421760</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6619117</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Forshaga</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Övre Ullerud</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2015-07-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2015-07-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ängen söder om korsningen</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Gustafsson, Jenny Sander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>54203200</v>
+      </c>
+      <c r="B7" t="n">
+        <v>43378</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>201075</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Brunfläckig pärlemorfjäril</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Boloria selene</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>T-korsningen norr om Örtenbråten, Mölnbackaområdet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>421760</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6619117</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Forshaga</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Övre Ullerud</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2015-07-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2015-07-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ängen söder om korsningen</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Per Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Per Gustafsson, Jenny Sander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133746318</v>
+      </c>
+      <c r="B8" t="n">
+        <v>107943</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219933</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kattfot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Antennaria dioica</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Forshaga, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>421623</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6618956</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Forshaga</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Övre Ullerud</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Fredric Stävenborg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Fredric Stävenborg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51072-2021 artfynd.xlsx
+++ b/artfynd/A 51072-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60096839</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94363122</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54203208</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1138,6 +1158,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60096832</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1253,6 +1278,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54203219</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1368,6 +1398,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54203200</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1475,8 +1510,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133746318</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>